--- a/Plantilla_Mediciones_Cobertura_REVISADA.xlsx
+++ b/Plantilla_Mediciones_Cobertura_REVISADA.xlsx
@@ -8,13 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Revisión idoneidad" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Mediciones movil" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Fibra y WiFi" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="LoRaWAN" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Backbone Ayto" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Resumen KPIs" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Leyenda" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Itinerario corregido" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cambios aplicados" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Mediciones movil" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fibra y WiFi" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="LoRaWAN" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Backbone Ayto" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Resumen KPIs" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Leyenda" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,8 +122,13 @@
       <sz val="10"/>
     </font>
     <font/>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -196,6 +202,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
@@ -207,16 +218,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE5CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E6D0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -307,17 +308,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -337,15 +329,18 @@
     <xf numFmtId="0" fontId="19" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -967,45 +962,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
-          <t>REVISIÓN DE IDONEIDAD DE LOS PUNTOS DE MEDICIÓN</t>
+          <t>ITINERARIO CORREGIDO DE PUNTOS DE MEDICIÓN</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="28" t="inlineStr">
         <is>
-          <t>Análisis de los 80 puntos propuestos frente al límite municipal oficial de Níjar (OpenStreetMap) y a la accesibilidad. Coordenadas de referencia APROXIMADAS por núcleo/hito: validar con GPS en campo. IT DIGITTAL · Exp. 18962/2025.</t>
+          <t>80 puntos, todos dentro del término municipal de Níjar. Se sustituyeron 13 puntos que quedaban fuera (zona Cabo de Gata/Almería) y se reubicaron 6 de acceso difícil. Coordenadas de referencia APROXIMADAS (validar con GPS en campo). IT DIGITTAL · Exp. 18962/2025.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="29" t="inlineStr">
         <is>
-          <t>Resumen:  OK=47   ·   Acceso medio (confirmar)=14   ·   Acceso difícil=6   ·   FUERA del término (Almería)=13</t>
+          <t>Resumen:  Acceso OK=64   ·   Acceso medio (confirmar)=16   ·   Sustitutos nuevos=13   ·   Reubicados=6   ·   Fuera de término=0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="30" t="inlineStr">
         <is>
-          <t>ID Punto</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B5" s="30" t="inlineStr">
@@ -1045,7 +1041,12 @@
       </c>
       <c r="I5" s="30" t="inlineStr">
         <is>
-          <t>Acción propuesta / Motivo</t>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="J5" s="30" t="inlineStr">
+        <is>
+          <t>Origen (punto anterior)</t>
         </is>
       </c>
     </row>
@@ -1074,21 +1075,22 @@
       <c r="F6" s="32" t="n">
         <v>-2.2076</v>
       </c>
-      <c r="G6" s="33" t="inlineStr">
+      <c r="G6" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H6" s="33" t="inlineStr">
+      <c r="H6" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I6" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I6" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J6" s="32" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
@@ -1115,21 +1117,22 @@
       <c r="F7" s="32" t="n">
         <v>-2.2071</v>
       </c>
-      <c r="G7" s="33" t="inlineStr">
+      <c r="G7" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H7" s="33" t="inlineStr">
+      <c r="H7" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I7" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I7" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J7" s="32" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="31" t="inlineStr">
@@ -1156,21 +1159,22 @@
       <c r="F8" s="32" t="n">
         <v>-2.2088</v>
       </c>
-      <c r="G8" s="33" t="inlineStr">
+      <c r="G8" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H8" s="33" t="inlineStr">
+      <c r="H8" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I8" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J8" s="32" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
@@ -1197,21 +1201,22 @@
       <c r="F9" s="32" t="n">
         <v>-2.2065</v>
       </c>
-      <c r="G9" s="33" t="inlineStr">
+      <c r="G9" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H9" s="33" t="inlineStr">
+      <c r="H9" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I9" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I9" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J9" s="32" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
@@ -1238,21 +1243,22 @@
       <c r="F10" s="32" t="n">
         <v>-2.2058</v>
       </c>
-      <c r="G10" s="33" t="inlineStr">
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H10" s="33" t="inlineStr">
+      <c r="H10" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I10" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J10" s="32" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
@@ -1279,21 +1285,22 @@
       <c r="F11" s="32" t="n">
         <v>-2.207</v>
       </c>
-      <c r="G11" s="33" t="inlineStr">
+      <c r="G11" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H11" s="33" t="inlineStr">
+      <c r="H11" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I11" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I11" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J11" s="32" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="34" t="inlineStr">
@@ -1320,21 +1327,22 @@
       <c r="F12" s="35" t="n">
         <v>-2.1741</v>
       </c>
-      <c r="G12" s="36" t="inlineStr">
+      <c r="G12" s="35" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H12" s="36" t="inlineStr">
+      <c r="H12" s="35" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I12" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRMAR ACCESO — Aldea de montaña; carretera estrecha y sinuosa</t>
-        </is>
-      </c>
+      <c r="I12" s="36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J12" s="35" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
@@ -1361,21 +1369,22 @@
       <c r="F13" s="32" t="n">
         <v>-2.1462</v>
       </c>
-      <c r="G13" s="33" t="inlineStr">
+      <c r="G13" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H13" s="33" t="inlineStr">
+      <c r="H13" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I13" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J13" s="32" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="31" t="inlineStr">
@@ -1402,21 +1411,22 @@
       <c r="F14" s="32" t="n">
         <v>-2.1055</v>
       </c>
-      <c r="G14" s="33" t="inlineStr">
+      <c r="G14" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H14" s="33" t="inlineStr">
+      <c r="H14" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I14" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J14" s="32" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
@@ -1443,21 +1453,22 @@
       <c r="F15" s="32" t="n">
         <v>-2.1075</v>
       </c>
-      <c r="G15" s="33" t="inlineStr">
+      <c r="G15" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H15" s="33" t="inlineStr">
+      <c r="H15" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I15" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J15" s="32" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="31" t="inlineStr">
@@ -1484,21 +1495,22 @@
       <c r="F16" s="32" t="n">
         <v>-2.1045</v>
       </c>
-      <c r="G16" s="33" t="inlineStr">
+      <c r="G16" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H16" s="33" t="inlineStr">
+      <c r="H16" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I16" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I16" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J16" s="32" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
@@ -1525,21 +1537,22 @@
       <c r="F17" s="32" t="n">
         <v>-2.111</v>
       </c>
-      <c r="G17" s="33" t="inlineStr">
+      <c r="G17" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H17" s="33" t="inlineStr">
+      <c r="H17" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I17" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I17" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J17" s="32" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="34" t="inlineStr">
@@ -1566,21 +1579,22 @@
       <c r="F18" s="35" t="n">
         <v>-2.125</v>
       </c>
-      <c r="G18" s="36" t="inlineStr">
+      <c r="G18" s="35" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H18" s="36" t="inlineStr">
+      <c r="H18" s="35" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I18" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRMAR ACCESO — Aparcamiento con restricción de vehículos en temporada alta</t>
-        </is>
-      </c>
+      <c r="I18" s="36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J18" s="35" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="37" t="inlineStr">
@@ -1598,28 +1612,33 @@
       </c>
       <c r="D19" s="38" t="inlineStr">
         <is>
-          <t>Playa Mónsul (orilla)</t>
+          <t>Mirador de carretera (acceso accesible)</t>
         </is>
       </c>
       <c r="E19" s="38" t="n">
-        <v>36.73</v>
+        <v>36.7395</v>
       </c>
       <c r="F19" s="38" t="n">
-        <v>-2.129</v>
-      </c>
-      <c r="G19" s="39" t="inlineStr">
+        <v>-2.1195</v>
+      </c>
+      <c r="G19" s="38" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H19" s="39" t="inlineStr">
-        <is>
-          <t>Difícil</t>
-        </is>
-      </c>
-      <c r="I19" s="38" t="inlineStr">
-        <is>
-          <t>REUBICAR / DESCARTAR — Acceso difícil. Playa protegida; en verano solo bus/bici/pie (acceso rodado cortado)</t>
+      <c r="H19" s="38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I19" s="37" t="inlineStr">
+        <is>
+          <t>REUBICADO</t>
+        </is>
+      </c>
+      <c r="J19" s="38" t="inlineStr">
+        <is>
+          <t>Mónsul · Playa Mónsul (orilla)</t>
         </is>
       </c>
     </row>
@@ -1639,28 +1658,33 @@
       </c>
       <c r="D20" s="38" t="inlineStr">
         <is>
-          <t>Playa Genoveses</t>
+          <t>Entrada/mirador norte (accesible)</t>
         </is>
       </c>
       <c r="E20" s="38" t="n">
-        <v>36.746</v>
+        <v>36.7555</v>
       </c>
       <c r="F20" s="38" t="n">
-        <v>-2.123</v>
-      </c>
-      <c r="G20" s="39" t="inlineStr">
+        <v>-2.1145</v>
+      </c>
+      <c r="G20" s="38" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H20" s="39" t="inlineStr">
-        <is>
-          <t>Difícil</t>
-        </is>
-      </c>
-      <c r="I20" s="38" t="inlineStr">
-        <is>
-          <t>REUBICAR / DESCARTAR — Acceso difícil. Playa protegida; en verano solo bus/bici/pie (acceso rodado cortado)</t>
+      <c r="H20" s="38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I20" s="37" t="inlineStr">
+        <is>
+          <t>REUBICADO</t>
+        </is>
+      </c>
+      <c r="J20" s="38" t="inlineStr">
+        <is>
+          <t>Genoveses · Playa Genoveses</t>
         </is>
       </c>
     </row>
@@ -1689,21 +1713,22 @@
       <c r="F21" s="35" t="n">
         <v>-2.12</v>
       </c>
-      <c r="G21" s="36" t="inlineStr">
+      <c r="G21" s="35" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H21" s="36" t="inlineStr">
+      <c r="H21" s="35" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I21" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRMAR ACCESO — Aparcamiento con restricción estacional</t>
-        </is>
-      </c>
+      <c r="I21" s="36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J21" s="35" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
@@ -1730,21 +1755,22 @@
       <c r="F22" s="32" t="n">
         <v>-2.07</v>
       </c>
-      <c r="G22" s="33" t="inlineStr">
+      <c r="G22" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H22" s="33" t="inlineStr">
+      <c r="H22" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I22" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I22" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J22" s="32" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="34" t="inlineStr">
@@ -1771,21 +1797,22 @@
       <c r="F23" s="35" t="n">
         <v>-2.066</v>
       </c>
-      <c r="G23" s="36" t="inlineStr">
+      <c r="G23" s="35" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H23" s="36" t="inlineStr">
+      <c r="H23" s="35" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I23" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRMAR ACCESO — Castillo junto a la playa; tramo final a pie</t>
-        </is>
-      </c>
+      <c r="I23" s="36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J23" s="35" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="31" t="inlineStr">
@@ -1812,21 +1839,22 @@
       <c r="F24" s="32" t="n">
         <v>-2.103</v>
       </c>
-      <c r="G24" s="33" t="inlineStr">
+      <c r="G24" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H24" s="33" t="inlineStr">
+      <c r="H24" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I24" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I24" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J24" s="32" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
@@ -1853,21 +1881,22 @@
       <c r="F25" s="32" t="n">
         <v>-2.12</v>
       </c>
-      <c r="G25" s="33" t="inlineStr">
+      <c r="G25" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H25" s="33" t="inlineStr">
+      <c r="H25" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I25" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I25" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J25" s="32" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
@@ -1894,21 +1923,22 @@
       <c r="F26" s="32" t="n">
         <v>-2.106</v>
       </c>
-      <c r="G26" s="33" t="inlineStr">
+      <c r="G26" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H26" s="33" t="inlineStr">
+      <c r="H26" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I26" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I26" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J26" s="32" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
@@ -1935,21 +1965,22 @@
       <c r="F27" s="32" t="n">
         <v>-2.107</v>
       </c>
-      <c r="G27" s="33" t="inlineStr">
+      <c r="G27" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H27" s="33" t="inlineStr">
+      <c r="H27" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I27" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I27" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J27" s="32" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
@@ -1976,21 +2007,22 @@
       <c r="F28" s="32" t="n">
         <v>-2.048</v>
       </c>
-      <c r="G28" s="33" t="inlineStr">
+      <c r="G28" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H28" s="33" t="inlineStr">
+      <c r="H28" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I28" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I28" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J28" s="32" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="31" t="inlineStr">
@@ -2017,21 +2049,22 @@
       <c r="F29" s="32" t="n">
         <v>-2.047</v>
       </c>
-      <c r="G29" s="33" t="inlineStr">
+      <c r="G29" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H29" s="33" t="inlineStr">
+      <c r="H29" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I29" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I29" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J29" s="32" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="31" t="inlineStr">
@@ -2058,21 +2091,22 @@
       <c r="F30" s="32" t="n">
         <v>-2.135</v>
       </c>
-      <c r="G30" s="33" t="inlineStr">
+      <c r="G30" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H30" s="33" t="inlineStr">
+      <c r="H30" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I30" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I30" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J30" s="32" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="31" t="inlineStr">
@@ -2099,21 +2133,22 @@
       <c r="F31" s="32" t="n">
         <v>-2.008</v>
       </c>
-      <c r="G31" s="33" t="inlineStr">
+      <c r="G31" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H31" s="33" t="inlineStr">
+      <c r="H31" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I31" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I31" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J31" s="32" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="31" t="inlineStr">
@@ -2140,21 +2175,22 @@
       <c r="F32" s="32" t="n">
         <v>-2.006</v>
       </c>
-      <c r="G32" s="33" t="inlineStr">
+      <c r="G32" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H32" s="33" t="inlineStr">
+      <c r="H32" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I32" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I32" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J32" s="32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="37" t="inlineStr">
@@ -2172,28 +2208,33 @@
       </c>
       <c r="D33" s="38" t="inlineStr">
         <is>
-          <t>Acceso pista San Pedro</t>
+          <t>Aparcamiento/mirador norte (fin de asfalto)</t>
         </is>
       </c>
       <c r="E33" s="38" t="n">
-        <v>36.8955</v>
+        <v>36.8905</v>
       </c>
       <c r="F33" s="38" t="n">
-        <v>-2.0005</v>
-      </c>
-      <c r="G33" s="39" t="inlineStr">
+        <v>-2.005</v>
+      </c>
+      <c r="G33" s="38" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H33" s="39" t="inlineStr">
-        <is>
-          <t>Difícil</t>
-        </is>
-      </c>
-      <c r="I33" s="38" t="inlineStr">
-        <is>
-          <t>REUBICAR / DESCARTAR — Acceso difícil. Pista de tierra hacia Cala San Pedro; no apta para turismo</t>
+      <c r="H33" s="38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I33" s="37" t="inlineStr">
+        <is>
+          <t>REUBICADO</t>
+        </is>
+      </c>
+      <c r="J33" s="38" t="inlineStr">
+        <is>
+          <t>Las Negras · Acceso pista San Pedro</t>
         </is>
       </c>
     </row>
@@ -2208,33 +2249,38 @@
       </c>
       <c r="C34" s="38" t="inlineStr">
         <is>
-          <t>Cala San Pedro</t>
+          <t>Las Negras</t>
         </is>
       </c>
       <c r="D34" s="38" t="inlineStr">
         <is>
-          <t>Cala virgen (sin acceso vehículo)</t>
+          <t>Puerto/embarcadero (salida a Cala San Pedro)</t>
         </is>
       </c>
       <c r="E34" s="38" t="n">
-        <v>36.9065</v>
+        <v>36.8872</v>
       </c>
       <c r="F34" s="38" t="n">
-        <v>-1.995</v>
-      </c>
-      <c r="G34" s="39" t="inlineStr">
+        <v>-2.0068</v>
+      </c>
+      <c r="G34" s="38" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H34" s="39" t="inlineStr">
-        <is>
-          <t>Difícil</t>
-        </is>
-      </c>
-      <c r="I34" s="38" t="inlineStr">
-        <is>
-          <t>REUBICAR / DESCARTAR — Acceso difícil. Cala virgen SIN acceso rodado: solo a pie (~1 h) o en barco</t>
+      <c r="H34" s="38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I34" s="37" t="inlineStr">
+        <is>
+          <t>REUBICADO</t>
+        </is>
+      </c>
+      <c r="J34" s="38" t="inlineStr">
+        <is>
+          <t>Cala San Pedro · Cala virgen (sin acceso vehículo)</t>
         </is>
       </c>
     </row>
@@ -2263,21 +2309,22 @@
       <c r="F35" s="32" t="n">
         <v>-2.01</v>
       </c>
-      <c r="G35" s="33" t="inlineStr">
+      <c r="G35" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H35" s="33" t="inlineStr">
+      <c r="H35" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I35" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I35" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J35" s="32" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="31" t="inlineStr">
@@ -2304,21 +2351,22 @@
       <c r="F36" s="32" t="n">
         <v>-2.0065</v>
       </c>
-      <c r="G36" s="33" t="inlineStr">
+      <c r="G36" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H36" s="33" t="inlineStr">
+      <c r="H36" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I36" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I36" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J36" s="32" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="34" t="inlineStr">
@@ -2345,21 +2393,22 @@
       <c r="F37" s="35" t="n">
         <v>-2.03</v>
       </c>
-      <c r="G37" s="36" t="inlineStr">
+      <c r="G37" s="35" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H37" s="36" t="inlineStr">
+      <c r="H37" s="35" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I37" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRMAR ACCESO — Tramo de carretera; parada solo en apartaderos</t>
-        </is>
-      </c>
+      <c r="I37" s="36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J37" s="35" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="31" t="inlineStr">
@@ -2386,21 +2435,22 @@
       <c r="F38" s="32" t="n">
         <v>-1.939</v>
       </c>
-      <c r="G38" s="33" t="inlineStr">
+      <c r="G38" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H38" s="33" t="inlineStr">
+      <c r="H38" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I38" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I38" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J38" s="32" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="31" t="inlineStr">
@@ -2427,21 +2477,22 @@
       <c r="F39" s="32" t="n">
         <v>-1.938</v>
       </c>
-      <c r="G39" s="33" t="inlineStr">
+      <c r="G39" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H39" s="33" t="inlineStr">
+      <c r="H39" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I39" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I39" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J39" s="32" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="37" t="inlineStr">
@@ -2454,33 +2505,38 @@
       </c>
       <c r="C40" s="38" t="inlineStr">
         <is>
-          <t>Cala Enmedio</t>
+          <t>Agua Amarga</t>
         </is>
       </c>
       <c r="D40" s="38" t="inlineStr">
         <is>
-          <t>Punto acceso peatonal</t>
+          <t>Aparcamiento sur (inicio sendero Cala Enmedio)</t>
         </is>
       </c>
       <c r="E40" s="38" t="n">
-        <v>36.927</v>
+        <v>36.9375</v>
       </c>
       <c r="F40" s="38" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="G40" s="39" t="inlineStr">
+        <v>-1.9345</v>
+      </c>
+      <c r="G40" s="38" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H40" s="39" t="inlineStr">
-        <is>
-          <t>Difícil</t>
-        </is>
-      </c>
-      <c r="I40" s="38" t="inlineStr">
-        <is>
-          <t>REUBICAR / DESCARTAR — Acceso difícil. Cala solo a pie desde Agua Amarga (~30-40 min)</t>
+      <c r="H40" s="38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I40" s="37" t="inlineStr">
+        <is>
+          <t>REUBICADO</t>
+        </is>
+      </c>
+      <c r="J40" s="38" t="inlineStr">
+        <is>
+          <t>Cala Enmedio · Punto acceso peatonal</t>
         </is>
       </c>
     </row>
@@ -2495,33 +2551,38 @@
       </c>
       <c r="C41" s="38" t="inlineStr">
         <is>
-          <t>Cala Enmedio</t>
+          <t>Agua Amarga</t>
         </is>
       </c>
       <c r="D41" s="38" t="inlineStr">
         <is>
-          <t>Cala virgen mirador</t>
+          <t>Mirador/zona hotelera sur (accesible)</t>
         </is>
       </c>
       <c r="E41" s="38" t="n">
-        <v>36.925</v>
+        <v>36.9388</v>
       </c>
       <c r="F41" s="38" t="n">
-        <v>-1.918</v>
-      </c>
-      <c r="G41" s="39" t="inlineStr">
+        <v>-1.9368</v>
+      </c>
+      <c r="G41" s="38" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H41" s="39" t="inlineStr">
-        <is>
-          <t>Difícil</t>
-        </is>
-      </c>
-      <c r="I41" s="38" t="inlineStr">
-        <is>
-          <t>REUBICAR / DESCARTAR — Acceso difícil. Mirador de cala virgen; acceso peatonal por sendero</t>
+      <c r="H41" s="38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I41" s="37" t="inlineStr">
+        <is>
+          <t>REUBICADO</t>
+        </is>
+      </c>
+      <c r="J41" s="38" t="inlineStr">
+        <is>
+          <t>Cala Enmedio · Cala virgen mirador</t>
         </is>
       </c>
     </row>
@@ -2550,21 +2611,22 @@
       <c r="F42" s="35" t="n">
         <v>-1.911</v>
       </c>
-      <c r="G42" s="36" t="inlineStr">
+      <c r="G42" s="35" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H42" s="36" t="inlineStr">
+      <c r="H42" s="35" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I42" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRMAR ACCESO — Faro/mirador con acceso restringido; pista final</t>
-        </is>
-      </c>
+      <c r="I42" s="36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J42" s="35" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="31" t="inlineStr">
@@ -2591,21 +2653,22 @@
       <c r="F43" s="32" t="n">
         <v>-1.94</v>
       </c>
-      <c r="G43" s="33" t="inlineStr">
+      <c r="G43" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H43" s="33" t="inlineStr">
+      <c r="H43" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I43" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I43" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J43" s="32" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="31" t="inlineStr">
@@ -2632,21 +2695,22 @@
       <c r="F44" s="32" t="n">
         <v>-1.9395</v>
       </c>
-      <c r="G44" s="33" t="inlineStr">
+      <c r="G44" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H44" s="33" t="inlineStr">
+      <c r="H44" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I44" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I44" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J44" s="32" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="31" t="inlineStr">
@@ -2673,21 +2737,22 @@
       <c r="F45" s="32" t="n">
         <v>-1.9388</v>
       </c>
-      <c r="G45" s="33" t="inlineStr">
+      <c r="G45" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H45" s="33" t="inlineStr">
+      <c r="H45" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I45" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I45" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J45" s="32" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="31" t="inlineStr">
@@ -2714,21 +2779,22 @@
       <c r="F46" s="32" t="n">
         <v>-1.96</v>
       </c>
-      <c r="G46" s="33" t="inlineStr">
+      <c r="G46" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H46" s="33" t="inlineStr">
+      <c r="H46" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I46" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I46" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J46" s="32" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="31" t="inlineStr">
@@ -2755,21 +2821,22 @@
       <c r="F47" s="32" t="n">
         <v>-2.038</v>
       </c>
-      <c r="G47" s="33" t="inlineStr">
+      <c r="G47" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H47" s="33" t="inlineStr">
+      <c r="H47" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I47" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I47" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J47" s="32" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="31" t="inlineStr">
@@ -2796,21 +2863,22 @@
       <c r="F48" s="32" t="n">
         <v>-2.0375</v>
       </c>
-      <c r="G48" s="33" t="inlineStr">
+      <c r="G48" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H48" s="33" t="inlineStr">
+      <c r="H48" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I48" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I48" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J48" s="32" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="31" t="inlineStr">
@@ -2837,21 +2905,22 @@
       <c r="F49" s="32" t="n">
         <v>-2.0378</v>
       </c>
-      <c r="G49" s="33" t="inlineStr">
+      <c r="G49" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H49" s="33" t="inlineStr">
+      <c r="H49" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I49" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I49" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J49" s="32" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="31" t="inlineStr">
@@ -2878,21 +2947,22 @@
       <c r="F50" s="32" t="n">
         <v>-2.0382</v>
       </c>
-      <c r="G50" s="33" t="inlineStr">
+      <c r="G50" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H50" s="33" t="inlineStr">
+      <c r="H50" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I50" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I50" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J50" s="32" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="31" t="inlineStr">
@@ -2919,21 +2989,22 @@
       <c r="F51" s="32" t="n">
         <v>-2.0372</v>
       </c>
-      <c r="G51" s="33" t="inlineStr">
+      <c r="G51" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H51" s="33" t="inlineStr">
+      <c r="H51" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I51" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I51" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J51" s="32" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="34" t="inlineStr">
@@ -2960,21 +3031,22 @@
       <c r="F52" s="35" t="n">
         <v>-2.0205</v>
       </c>
-      <c r="G52" s="36" t="inlineStr">
+      <c r="G52" s="35" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H52" s="36" t="inlineStr">
+      <c r="H52" s="35" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I52" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRMAR ACCESO — Playa El Playazo; pista de acceso de tierra</t>
-        </is>
-      </c>
+      <c r="I52" s="36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J52" s="35" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="34" t="inlineStr">
@@ -3001,21 +3073,22 @@
       <c r="F53" s="35" t="n">
         <v>-2.0185</v>
       </c>
-      <c r="G53" s="36" t="inlineStr">
+      <c r="G53" s="35" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H53" s="36" t="inlineStr">
+      <c r="H53" s="35" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I53" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRMAR ACCESO — Castillo junto a El Playazo; tramo a pie</t>
-        </is>
-      </c>
+      <c r="I53" s="36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J53" s="35" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="34" t="inlineStr">
@@ -3042,21 +3115,22 @@
       <c r="F54" s="35" t="n">
         <v>-2.045</v>
       </c>
-      <c r="G54" s="36" t="inlineStr">
+      <c r="G54" s="35" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H54" s="36" t="inlineStr">
+      <c r="H54" s="35" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I54" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRMAR ACCESO — Ruta ciclista por pista; sin acceso rodado normal</t>
-        </is>
-      </c>
+      <c r="I54" s="36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J54" s="35" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="34" t="inlineStr">
@@ -3083,21 +3157,22 @@
       <c r="F55" s="35" t="n">
         <v>-2.055</v>
       </c>
-      <c r="G55" s="36" t="inlineStr">
+      <c r="G55" s="35" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H55" s="36" t="inlineStr">
+      <c r="H55" s="35" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I55" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRMAR ACCESO — Ruta ciclista por pista</t>
-        </is>
-      </c>
+      <c r="I55" s="36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J55" s="35" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="34" t="inlineStr">
@@ -3124,21 +3199,22 @@
       <c r="F56" s="35" t="n">
         <v>-2.068</v>
       </c>
-      <c r="G56" s="36" t="inlineStr">
+      <c r="G56" s="35" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H56" s="36" t="inlineStr">
+      <c r="H56" s="35" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I56" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRMAR ACCESO — Ruta ciclista por pista</t>
-        </is>
-      </c>
+      <c r="I56" s="36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J56" s="35" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="34" t="inlineStr">
@@ -3165,21 +3241,22 @@
       <c r="F57" s="35" t="n">
         <v>-2.08</v>
       </c>
-      <c r="G57" s="36" t="inlineStr">
+      <c r="G57" s="35" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H57" s="36" t="inlineStr">
+      <c r="H57" s="35" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I57" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRMAR ACCESO — Ruta ciclista por pista</t>
-        </is>
-      </c>
+      <c r="I57" s="36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J57" s="35" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="34" t="inlineStr">
@@ -3206,21 +3283,22 @@
       <c r="F58" s="35" t="n">
         <v>-2.09</v>
       </c>
-      <c r="G58" s="36" t="inlineStr">
+      <c r="G58" s="35" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H58" s="36" t="inlineStr">
+      <c r="H58" s="35" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I58" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRMAR ACCESO — Ruta ciclista por pista</t>
-        </is>
-      </c>
+      <c r="I58" s="36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J58" s="35" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="31" t="inlineStr">
@@ -3247,21 +3325,22 @@
       <c r="F59" s="32" t="n">
         <v>-2.098</v>
       </c>
-      <c r="G59" s="33" t="inlineStr">
+      <c r="G59" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H59" s="33" t="inlineStr">
+      <c r="H59" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I59" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I59" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J59" s="32" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="31" t="inlineStr">
@@ -3288,21 +3367,22 @@
       <c r="F60" s="32" t="n">
         <v>-2.0982</v>
       </c>
-      <c r="G60" s="33" t="inlineStr">
+      <c r="G60" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H60" s="33" t="inlineStr">
+      <c r="H60" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I60" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I60" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J60" s="32" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="31" t="inlineStr">
@@ -3329,429 +3409,480 @@
       <c r="F61" s="32" t="n">
         <v>-2.0975</v>
       </c>
-      <c r="G61" s="33" t="inlineStr">
+      <c r="G61" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H61" s="33" t="inlineStr">
+      <c r="H61" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I61" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I61" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J61" s="32" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="40" t="inlineStr">
+      <c r="A62" s="37" t="inlineStr">
         <is>
           <t>P57-D6</t>
         </is>
       </c>
-      <c r="B62" s="41" t="n">
+      <c r="B62" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="41" t="inlineStr">
-        <is>
-          <t>Cabo de Gata pueblo</t>
-        </is>
-      </c>
-      <c r="D62" s="41" t="inlineStr">
-        <is>
-          <t>Plaza pueblo</t>
-        </is>
-      </c>
-      <c r="E62" s="41" t="n">
-        <v>36.789</v>
-      </c>
-      <c r="F62" s="41" t="n">
-        <v>-2.236</v>
-      </c>
-      <c r="G62" s="42" t="inlineStr">
-        <is>
-          <t>Fuera (Almería)</t>
-        </is>
-      </c>
-      <c r="H62" s="42" t="inlineStr">
+      <c r="C62" s="38" t="inlineStr">
+        <is>
+          <t>El Barranquete</t>
+        </is>
+      </c>
+      <c r="D62" s="38" t="inlineStr">
+        <is>
+          <t>Núcleo · pedanía Campo de Níjar</t>
+        </is>
+      </c>
+      <c r="E62" s="38" t="n">
+        <v>36.8381</v>
+      </c>
+      <c r="F62" s="38" t="n">
+        <v>-2.1971</v>
+      </c>
+      <c r="G62" s="38" t="inlineStr">
+        <is>
+          <t>Níjar</t>
+        </is>
+      </c>
+      <c r="H62" s="38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I62" s="41" t="inlineStr">
-        <is>
-          <t>DESCARTAR / SUSTITUIR — Fuera del término municipal de Níjar (pertenece a Almería). Reemplazar por un punto equivalente dentro de Níjar.</t>
+      <c r="I62" s="37" t="inlineStr">
+        <is>
+          <t>NUEVO (sustituto)</t>
+        </is>
+      </c>
+      <c r="J62" s="38" t="inlineStr">
+        <is>
+          <t>Cabo de Gata pueblo · Plaza pueblo</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="40" t="inlineStr">
+      <c r="A63" s="37" t="inlineStr">
         <is>
           <t>P58-D6</t>
         </is>
       </c>
-      <c r="B63" s="41" t="n">
+      <c r="B63" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="C63" s="41" t="inlineStr">
-        <is>
-          <t>Cabo de Gata pueblo</t>
-        </is>
-      </c>
-      <c r="D63" s="41" t="inlineStr">
-        <is>
-          <t>Almadraba Monteleva</t>
-        </is>
-      </c>
-      <c r="E63" s="41" t="n">
-        <v>36.775</v>
-      </c>
-      <c r="F63" s="41" t="n">
-        <v>-2.228</v>
-      </c>
-      <c r="G63" s="42" t="inlineStr">
-        <is>
-          <t>Fuera (Almería)</t>
-        </is>
-      </c>
-      <c r="H63" s="42" t="inlineStr">
+      <c r="C63" s="38" t="inlineStr">
+        <is>
+          <t>Ruescas</t>
+        </is>
+      </c>
+      <c r="D63" s="38" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
+        </is>
+      </c>
+      <c r="E63" s="38" t="n">
+        <v>36.8162</v>
+      </c>
+      <c r="F63" s="38" t="n">
+        <v>-2.2246</v>
+      </c>
+      <c r="G63" s="38" t="inlineStr">
+        <is>
+          <t>Níjar</t>
+        </is>
+      </c>
+      <c r="H63" s="38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I63" s="41" t="inlineStr">
-        <is>
-          <t>DESCARTAR / SUSTITUIR — Fuera del término municipal de Níjar (pertenece a Almería). Reemplazar por un punto equivalente dentro de Níjar.</t>
+      <c r="I63" s="37" t="inlineStr">
+        <is>
+          <t>NUEVO (sustituto)</t>
+        </is>
+      </c>
+      <c r="J63" s="38" t="inlineStr">
+        <is>
+          <t>Cabo de Gata pueblo · Almadraba Monteleva</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="40" t="inlineStr">
+      <c r="A64" s="37" t="inlineStr">
         <is>
           <t>P59-D6</t>
         </is>
       </c>
-      <c r="B64" s="41" t="n">
+      <c r="B64" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="C64" s="41" t="inlineStr">
-        <is>
-          <t>Cabo de Gata pueblo</t>
-        </is>
-      </c>
-      <c r="D64" s="41" t="inlineStr">
-        <is>
-          <t>Iglesia Almadraba</t>
-        </is>
-      </c>
-      <c r="E64" s="41" t="n">
-        <v>36.772</v>
-      </c>
-      <c r="F64" s="41" t="n">
-        <v>-2.227</v>
-      </c>
-      <c r="G64" s="42" t="inlineStr">
-        <is>
-          <t>Fuera (Almería)</t>
-        </is>
-      </c>
-      <c r="H64" s="42" t="inlineStr">
+      <c r="C64" s="38" t="inlineStr">
+        <is>
+          <t>El Viso</t>
+        </is>
+      </c>
+      <c r="D64" s="38" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
+        </is>
+      </c>
+      <c r="E64" s="38" t="n">
+        <v>36.8799</v>
+      </c>
+      <c r="F64" s="38" t="n">
+        <v>-2.2045</v>
+      </c>
+      <c r="G64" s="38" t="inlineStr">
+        <is>
+          <t>Níjar</t>
+        </is>
+      </c>
+      <c r="H64" s="38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I64" s="41" t="inlineStr">
-        <is>
-          <t>DESCARTAR / SUSTITUIR — Fuera del término municipal de Níjar (pertenece a Almería). Reemplazar por un punto equivalente dentro de Níjar.</t>
+      <c r="I64" s="37" t="inlineStr">
+        <is>
+          <t>NUEVO (sustituto)</t>
+        </is>
+      </c>
+      <c r="J64" s="38" t="inlineStr">
+        <is>
+          <t>Cabo de Gata pueblo · Iglesia Almadraba</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="40" t="inlineStr">
+      <c r="A65" s="37" t="inlineStr">
         <is>
           <t>P60-D6</t>
         </is>
       </c>
-      <c r="B65" s="41" t="n">
+      <c r="B65" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="C65" s="41" t="inlineStr">
-        <is>
-          <t>Salinas</t>
-        </is>
-      </c>
-      <c r="D65" s="41" t="inlineStr">
-        <is>
-          <t>Centro Visitantes Salinas</t>
-        </is>
-      </c>
-      <c r="E65" s="41" t="n">
-        <v>36.77</v>
-      </c>
-      <c r="F65" s="41" t="n">
-        <v>-2.225</v>
-      </c>
-      <c r="G65" s="42" t="inlineStr">
-        <is>
-          <t>Fuera (Almería)</t>
-        </is>
-      </c>
-      <c r="H65" s="42" t="inlineStr">
+      <c r="C65" s="38" t="inlineStr">
+        <is>
+          <t>Los Grillos</t>
+        </is>
+      </c>
+      <c r="D65" s="38" t="inlineStr">
+        <is>
+          <t>Núcleo (San Isidro de Níjar)</t>
+        </is>
+      </c>
+      <c r="E65" s="38" t="n">
+        <v>36.8919</v>
+      </c>
+      <c r="F65" s="38" t="n">
+        <v>-2.1933</v>
+      </c>
+      <c r="G65" s="38" t="inlineStr">
+        <is>
+          <t>Níjar</t>
+        </is>
+      </c>
+      <c r="H65" s="38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I65" s="41" t="inlineStr">
-        <is>
-          <t>DESCARTAR / SUSTITUIR — Fuera del término municipal de Níjar (pertenece a Almería). Reemplazar por un punto equivalente dentro de Níjar.</t>
+      <c r="I65" s="37" t="inlineStr">
+        <is>
+          <t>NUEVO (sustituto)</t>
+        </is>
+      </c>
+      <c r="J65" s="38" t="inlineStr">
+        <is>
+          <t>Salinas · Centro Visitantes Salinas</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="40" t="inlineStr">
+      <c r="A66" s="37" t="inlineStr">
         <is>
           <t>P61-D6</t>
         </is>
       </c>
-      <c r="B66" s="41" t="n">
+      <c r="B66" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="C66" s="41" t="inlineStr">
-        <is>
-          <t>Salinas</t>
-        </is>
-      </c>
-      <c r="D66" s="41" t="inlineStr">
-        <is>
-          <t>Mirador flamencos</t>
-        </is>
-      </c>
-      <c r="E66" s="41" t="n">
-        <v>36.765</v>
-      </c>
-      <c r="F66" s="41" t="n">
-        <v>-2.22</v>
-      </c>
-      <c r="G66" s="42" t="inlineStr">
-        <is>
-          <t>Fuera (Almería)</t>
-        </is>
-      </c>
-      <c r="H66" s="42" t="inlineStr">
+      <c r="C66" s="38" t="inlineStr">
+        <is>
+          <t>La Serrata</t>
+        </is>
+      </c>
+      <c r="D66" s="38" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
+        </is>
+      </c>
+      <c r="E66" s="38" t="n">
+        <v>36.8754</v>
+      </c>
+      <c r="F66" s="38" t="n">
+        <v>-2.1472</v>
+      </c>
+      <c r="G66" s="38" t="inlineStr">
+        <is>
+          <t>Níjar</t>
+        </is>
+      </c>
+      <c r="H66" s="38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I66" s="41" t="inlineStr">
-        <is>
-          <t>DESCARTAR / SUSTITUIR — Fuera del término municipal de Níjar (pertenece a Almería). Reemplazar por un punto equivalente dentro de Níjar.</t>
+      <c r="I66" s="37" t="inlineStr">
+        <is>
+          <t>NUEVO (sustituto)</t>
+        </is>
+      </c>
+      <c r="J66" s="38" t="inlineStr">
+        <is>
+          <t>Salinas · Mirador flamencos</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="40" t="inlineStr">
+      <c r="A67" s="37" t="inlineStr">
         <is>
           <t>P62-D6</t>
         </is>
       </c>
-      <c r="B67" s="41" t="n">
+      <c r="B67" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="C67" s="41" t="inlineStr">
-        <is>
-          <t>Faro Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D67" s="41" t="inlineStr">
-        <is>
-          <t>Faro extremo sur</t>
-        </is>
-      </c>
-      <c r="E67" s="41" t="n">
-        <v>36.722</v>
-      </c>
-      <c r="F67" s="41" t="n">
-        <v>-2.192</v>
-      </c>
-      <c r="G67" s="42" t="inlineStr">
-        <is>
-          <t>Fuera (Almería)</t>
-        </is>
-      </c>
-      <c r="H67" s="42" t="inlineStr">
+      <c r="C67" s="38" t="inlineStr">
+        <is>
+          <t>Boca de los Frailes</t>
+        </is>
+      </c>
+      <c r="D67" s="38" t="inlineStr">
+        <is>
+          <t>Núcleo rural (valle San José)</t>
+        </is>
+      </c>
+      <c r="E67" s="38" t="n">
+        <v>36.8056</v>
+      </c>
+      <c r="F67" s="38" t="n">
+        <v>-2.1328</v>
+      </c>
+      <c r="G67" s="38" t="inlineStr">
+        <is>
+          <t>Níjar</t>
+        </is>
+      </c>
+      <c r="H67" s="38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I67" s="37" t="inlineStr">
+        <is>
+          <t>NUEVO (sustituto)</t>
+        </is>
+      </c>
+      <c r="J67" s="38" t="inlineStr">
+        <is>
+          <t>Faro Cabo Gata · Faro extremo sur</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="37" t="inlineStr">
+        <is>
+          <t>P63-D6</t>
+        </is>
+      </c>
+      <c r="B68" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="C68" s="38" t="inlineStr">
+        <is>
+          <t>Presillas Bajas</t>
+        </is>
+      </c>
+      <c r="D68" s="38" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
+        </is>
+      </c>
+      <c r="E68" s="38" t="n">
+        <v>36.8154</v>
+      </c>
+      <c r="F68" s="38" t="n">
+        <v>-2.0931</v>
+      </c>
+      <c r="G68" s="38" t="inlineStr">
+        <is>
+          <t>Níjar</t>
+        </is>
+      </c>
+      <c r="H68" s="38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I68" s="37" t="inlineStr">
+        <is>
+          <t>NUEVO (sustituto)</t>
+        </is>
+      </c>
+      <c r="J68" s="38" t="inlineStr">
+        <is>
+          <t>Faro Cabo Gata · Mirador Vela Blanca</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="37" t="inlineStr">
+        <is>
+          <t>P64-D6</t>
+        </is>
+      </c>
+      <c r="B69" s="38" t="n">
+        <v>6</v>
+      </c>
+      <c r="C69" s="38" t="inlineStr">
+        <is>
+          <t>Cala Higuera</t>
+        </is>
+      </c>
+      <c r="D69" s="38" t="inlineStr">
+        <is>
+          <t>Cala accesible por camino de tierra desde San José</t>
+        </is>
+      </c>
+      <c r="E69" s="38" t="n">
+        <v>36.7653</v>
+      </c>
+      <c r="F69" s="38" t="n">
+        <v>-2.1083</v>
+      </c>
+      <c r="G69" s="38" t="inlineStr">
+        <is>
+          <t>Níjar</t>
+        </is>
+      </c>
+      <c r="H69" s="38" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I67" s="41" t="inlineStr">
-        <is>
-          <t>DESCARTAR / SUSTITUIR — Fuera del término municipal de Níjar (pertenece a Almería). Faro extremo sur; carretera hasta el faro</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="40" t="inlineStr">
-        <is>
-          <t>P63-D6</t>
-        </is>
-      </c>
-      <c r="B68" s="41" t="n">
+      <c r="I69" s="37" t="inlineStr">
+        <is>
+          <t>NUEVO (sustituto)</t>
+        </is>
+      </c>
+      <c r="J69" s="38" t="inlineStr">
+        <is>
+          <t>Playa Cabo Gata · Playa pueblo Cabo Gata</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="37" t="inlineStr">
+        <is>
+          <t>P65-D6</t>
+        </is>
+      </c>
+      <c r="B70" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="C68" s="41" t="inlineStr">
-        <is>
-          <t>Faro Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D68" s="41" t="inlineStr">
-        <is>
-          <t>Mirador Vela Blanca</t>
-        </is>
-      </c>
-      <c r="E68" s="41" t="n">
-        <v>36.718</v>
-      </c>
-      <c r="F68" s="41" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="G68" s="42" t="inlineStr">
-        <is>
-          <t>Fuera (Almería)</t>
-        </is>
-      </c>
-      <c r="H68" s="42" t="inlineStr">
-        <is>
-          <t>Difícil</t>
-        </is>
-      </c>
-      <c r="I68" s="41" t="inlineStr">
-        <is>
-          <t>DESCARTAR / SUSTITUIR — Fuera del término municipal de Níjar (pertenece a Almería). Vela Blanca: barrera; tramo solo a pie/bici</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="40" t="inlineStr">
-        <is>
-          <t>P64-D6</t>
-        </is>
-      </c>
-      <c r="B69" s="41" t="n">
+      <c r="C70" s="38" t="inlineStr">
+        <is>
+          <t>El Romeral</t>
+        </is>
+      </c>
+      <c r="D70" s="38" t="inlineStr">
+        <is>
+          <t>Núcleo norte del término</t>
+        </is>
+      </c>
+      <c r="E70" s="38" t="n">
+        <v>36.9923</v>
+      </c>
+      <c r="F70" s="38" t="n">
+        <v>-2.2346</v>
+      </c>
+      <c r="G70" s="38" t="inlineStr">
+        <is>
+          <t>Níjar</t>
+        </is>
+      </c>
+      <c r="H70" s="38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I70" s="37" t="inlineStr">
+        <is>
+          <t>NUEVO (sustituto)</t>
+        </is>
+      </c>
+      <c r="J70" s="38" t="inlineStr">
+        <is>
+          <t>Retamar · Núcleo Retamar (límite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="37" t="inlineStr">
+        <is>
+          <t>P66-D6</t>
+        </is>
+      </c>
+      <c r="B71" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="C69" s="41" t="inlineStr">
-        <is>
-          <t>Playa Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D69" s="41" t="inlineStr">
-        <is>
-          <t>Playa pueblo Cabo Gata</t>
-        </is>
-      </c>
-      <c r="E69" s="41" t="n">
-        <v>36.79</v>
-      </c>
-      <c r="F69" s="41" t="n">
-        <v>-2.23</v>
-      </c>
-      <c r="G69" s="42" t="inlineStr">
-        <is>
-          <t>Fuera (Almería)</t>
-        </is>
-      </c>
-      <c r="H69" s="42" t="inlineStr">
+      <c r="C71" s="38" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="D71" s="38" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
+        </is>
+      </c>
+      <c r="E71" s="38" t="n">
+        <v>36.9219</v>
+      </c>
+      <c r="F71" s="38" t="n">
+        <v>-2.0174</v>
+      </c>
+      <c r="G71" s="38" t="inlineStr">
+        <is>
+          <t>Níjar</t>
+        </is>
+      </c>
+      <c r="H71" s="38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I69" s="41" t="inlineStr">
-        <is>
-          <t>DESCARTAR / SUSTITUIR — Fuera del término municipal de Níjar (pertenece a Almería). Reemplazar por un punto equivalente dentro de Níjar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="40" t="inlineStr">
-        <is>
-          <t>P65-D6</t>
-        </is>
-      </c>
-      <c r="B70" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="C70" s="41" t="inlineStr">
-        <is>
-          <t>Retamar</t>
-        </is>
-      </c>
-      <c r="D70" s="41" t="inlineStr">
-        <is>
-          <t>Núcleo Retamar (límite)</t>
-        </is>
-      </c>
-      <c r="E70" s="41" t="n">
-        <v>36.834</v>
-      </c>
-      <c r="F70" s="41" t="n">
-        <v>-2.287</v>
-      </c>
-      <c r="G70" s="42" t="inlineStr">
-        <is>
-          <t>Fuera (Almería)</t>
-        </is>
-      </c>
-      <c r="H70" s="42" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I70" s="41" t="inlineStr">
-        <is>
-          <t>DESCARTAR / SUSTITUIR — Fuera del término municipal de Níjar (pertenece a Almería). Reemplazar por un punto equivalente dentro de Níjar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="40" t="inlineStr">
-        <is>
-          <t>P66-D6</t>
-        </is>
-      </c>
-      <c r="B71" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="C71" s="41" t="inlineStr">
-        <is>
-          <t>Pujaire</t>
-        </is>
-      </c>
-      <c r="D71" s="41" t="inlineStr">
-        <is>
-          <t>Núcleo Pujaire</t>
-        </is>
-      </c>
-      <c r="E71" s="41" t="n">
-        <v>36.805</v>
-      </c>
-      <c r="F71" s="41" t="n">
-        <v>-2.247</v>
-      </c>
-      <c r="G71" s="42" t="inlineStr">
-        <is>
-          <t>Fuera (Almería)</t>
-        </is>
-      </c>
-      <c r="H71" s="42" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I71" s="41" t="inlineStr">
-        <is>
-          <t>DESCARTAR / SUSTITUIR — Fuera del término municipal de Níjar (pertenece a Almería). Reemplazar por un punto equivalente dentro de Níjar.</t>
+      <c r="I71" s="37" t="inlineStr">
+        <is>
+          <t>NUEVO (sustituto)</t>
+        </is>
+      </c>
+      <c r="J71" s="38" t="inlineStr">
+        <is>
+          <t>Pujaire · Núcleo Pujaire</t>
         </is>
       </c>
     </row>
@@ -3780,60 +3911,66 @@
       <c r="F72" s="35" t="n">
         <v>-2.2</v>
       </c>
-      <c r="G72" s="36" t="inlineStr">
+      <c r="G72" s="35" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H72" s="36" t="inlineStr">
+      <c r="H72" s="35" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
-      <c r="I72" s="35" t="inlineStr">
-        <is>
-          <t>CONFIRMAR ACCESO — Tramo de carretera hacia el faro</t>
-        </is>
-      </c>
+      <c r="I72" s="36" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J72" s="35" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="40" t="inlineStr">
+      <c r="A73" s="37" t="inlineStr">
         <is>
           <t>P68-D6</t>
         </is>
       </c>
-      <c r="B73" s="41" t="n">
+      <c r="B73" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="C73" s="41" t="inlineStr">
-        <is>
-          <t>Camping Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D73" s="41" t="inlineStr">
-        <is>
-          <t>Camping municipal</t>
-        </is>
-      </c>
-      <c r="E73" s="41" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="F73" s="41" t="n">
-        <v>-2.243</v>
-      </c>
-      <c r="G73" s="42" t="inlineStr">
-        <is>
-          <t>Fuera (Almería)</t>
-        </is>
-      </c>
-      <c r="H73" s="42" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="I73" s="41" t="inlineStr">
-        <is>
-          <t>DESCARTAR / SUSTITUIR — Fuera del término municipal de Níjar (pertenece a Almería). Reemplazar por un punto equivalente dentro de Níjar.</t>
+      <c r="C73" s="38" t="inlineStr">
+        <is>
+          <t>Cortijo del Fraile</t>
+        </is>
+      </c>
+      <c r="D73" s="38" t="inlineStr">
+        <is>
+          <t>Monumento histórico (BIC) · pista de acceso</t>
+        </is>
+      </c>
+      <c r="E73" s="38" t="n">
+        <v>36.8656</v>
+      </c>
+      <c r="F73" s="38" t="n">
+        <v>-2.0748</v>
+      </c>
+      <c r="G73" s="38" t="inlineStr">
+        <is>
+          <t>Níjar</t>
+        </is>
+      </c>
+      <c r="H73" s="38" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="I73" s="37" t="inlineStr">
+        <is>
+          <t>NUEVO (sustituto)</t>
+        </is>
+      </c>
+      <c r="J73" s="38" t="inlineStr">
+        <is>
+          <t>Camping Cabo Gata · Camping municipal</t>
         </is>
       </c>
     </row>
@@ -3862,21 +3999,22 @@
       <c r="F74" s="32" t="n">
         <v>-2.1462</v>
       </c>
-      <c r="G74" s="33" t="inlineStr">
+      <c r="G74" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H74" s="33" t="inlineStr">
+      <c r="H74" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I74" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I74" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J74" s="32" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
@@ -3903,21 +4041,22 @@
       <c r="F75" s="32" t="n">
         <v>-2.108</v>
       </c>
-      <c r="G75" s="33" t="inlineStr">
+      <c r="G75" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H75" s="33" t="inlineStr">
+      <c r="H75" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I75" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I75" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J75" s="32" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="31" t="inlineStr">
@@ -3944,21 +4083,22 @@
       <c r="F76" s="32" t="n">
         <v>-2.083</v>
       </c>
-      <c r="G76" s="33" t="inlineStr">
+      <c r="G76" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H76" s="33" t="inlineStr">
+      <c r="H76" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I76" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I76" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J76" s="32" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="31" t="inlineStr">
@@ -3985,21 +4125,22 @@
       <c r="F77" s="32" t="n">
         <v>-2.033</v>
       </c>
-      <c r="G77" s="33" t="inlineStr">
+      <c r="G77" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H77" s="33" t="inlineStr">
+      <c r="H77" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I77" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I77" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J77" s="32" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="31" t="inlineStr">
@@ -4026,21 +4167,22 @@
       <c r="F78" s="32" t="n">
         <v>-2.12</v>
       </c>
-      <c r="G78" s="33" t="inlineStr">
+      <c r="G78" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H78" s="33" t="inlineStr">
+      <c r="H78" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I78" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I78" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J78" s="32" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="31" t="inlineStr">
@@ -4067,60 +4209,66 @@
       <c r="F79" s="32" t="n">
         <v>-2.06</v>
       </c>
-      <c r="G79" s="33" t="inlineStr">
+      <c r="G79" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H79" s="33" t="inlineStr">
+      <c r="H79" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I79" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I79" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J79" s="32" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="40" t="inlineStr">
+      <c r="A80" s="37" t="inlineStr">
         <is>
           <t>P75-D7</t>
         </is>
       </c>
-      <c r="B80" s="41" t="n">
+      <c r="B80" s="38" t="n">
         <v>7</v>
       </c>
-      <c r="C80" s="41" t="inlineStr">
-        <is>
-          <t>Pujaire</t>
-        </is>
-      </c>
-      <c r="D80" s="41" t="inlineStr">
-        <is>
-          <t>Pista a Cabo Gata</t>
-        </is>
-      </c>
-      <c r="E80" s="41" t="n">
-        <v>36.81</v>
-      </c>
-      <c r="F80" s="41" t="n">
-        <v>-2.245</v>
-      </c>
-      <c r="G80" s="42" t="inlineStr">
-        <is>
-          <t>Fuera (Almería)</t>
-        </is>
-      </c>
-      <c r="H80" s="42" t="inlineStr">
-        <is>
-          <t>Medio</t>
-        </is>
-      </c>
-      <c r="I80" s="41" t="inlineStr">
-        <is>
-          <t>DESCARTAR / SUSTITUIR — Fuera del término municipal de Níjar (pertenece a Almería). Pista de tierra hacia Cabo de Gata</t>
+      <c r="C80" s="38" t="inlineStr">
+        <is>
+          <t>Cala del Cuervo</t>
+        </is>
+      </c>
+      <c r="D80" s="38" t="inlineStr">
+        <is>
+          <t>Cala junto a la carretera de Las Negras</t>
+        </is>
+      </c>
+      <c r="E80" s="38" t="n">
+        <v>36.873</v>
+      </c>
+      <c r="F80" s="38" t="n">
+        <v>-2.0035</v>
+      </c>
+      <c r="G80" s="38" t="inlineStr">
+        <is>
+          <t>Níjar</t>
+        </is>
+      </c>
+      <c r="H80" s="38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I80" s="37" t="inlineStr">
+        <is>
+          <t>NUEVO (sustituto)</t>
+        </is>
+      </c>
+      <c r="J80" s="38" t="inlineStr">
+        <is>
+          <t>Pujaire · Pista a Cabo Gata</t>
         </is>
       </c>
     </row>
@@ -4149,21 +4297,22 @@
       <c r="F81" s="32" t="n">
         <v>-2.09</v>
       </c>
-      <c r="G81" s="33" t="inlineStr">
+      <c r="G81" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H81" s="33" t="inlineStr">
+      <c r="H81" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I81" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I81" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J81" s="32" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="31" t="inlineStr">
@@ -4190,60 +4339,66 @@
       <c r="F82" s="32" t="n">
         <v>-2.16</v>
       </c>
-      <c r="G82" s="33" t="inlineStr">
+      <c r="G82" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H82" s="33" t="inlineStr">
+      <c r="H82" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I82" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I82" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J82" s="32" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="40" t="inlineStr">
+      <c r="A83" s="37" t="inlineStr">
         <is>
           <t>P78-D7</t>
         </is>
       </c>
-      <c r="B83" s="41" t="n">
+      <c r="B83" s="38" t="n">
         <v>7</v>
       </c>
-      <c r="C83" s="41" t="inlineStr">
-        <is>
-          <t>Carretera N-340a</t>
-        </is>
-      </c>
-      <c r="D83" s="41" t="inlineStr">
-        <is>
-          <t>Tramo Níjar-Almería</t>
-        </is>
-      </c>
-      <c r="E83" s="41" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="F83" s="41" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="G83" s="42" t="inlineStr">
-        <is>
-          <t>Fuera (Almería)</t>
-        </is>
-      </c>
-      <c r="H83" s="42" t="inlineStr">
-        <is>
-          <t>Medio</t>
-        </is>
-      </c>
-      <c r="I83" s="41" t="inlineStr">
-        <is>
-          <t>DESCARTAR / SUSTITUIR — Fuera del término municipal de Níjar (pertenece a Almería). Tramo de carretera N-340a</t>
+      <c r="C83" s="38" t="inlineStr">
+        <is>
+          <t>Saladar y Leche</t>
+        </is>
+      </c>
+      <c r="D83" s="38" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
+        </is>
+      </c>
+      <c r="E83" s="38" t="n">
+        <v>36.9613</v>
+      </c>
+      <c r="F83" s="38" t="n">
+        <v>-2.0953</v>
+      </c>
+      <c r="G83" s="38" t="inlineStr">
+        <is>
+          <t>Níjar</t>
+        </is>
+      </c>
+      <c r="H83" s="38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I83" s="37" t="inlineStr">
+        <is>
+          <t>NUEVO (sustituto)</t>
+        </is>
+      </c>
+      <c r="J83" s="38" t="inlineStr">
+        <is>
+          <t>Carretera N-340a · Tramo Níjar-Almería</t>
         </is>
       </c>
     </row>
@@ -4272,21 +4427,22 @@
       <c r="F84" s="32" t="n">
         <v>-2.15</v>
       </c>
-      <c r="G84" s="33" t="inlineStr">
+      <c r="G84" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H84" s="33" t="inlineStr">
+      <c r="H84" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I84" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I84" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J84" s="32" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="31" t="inlineStr">
@@ -4313,32 +4469,536 @@
       <c r="F85" s="32" t="n">
         <v>-2.2073</v>
       </c>
-      <c r="G85" s="33" t="inlineStr">
+      <c r="G85" s="32" t="inlineStr">
         <is>
           <t>Níjar</t>
         </is>
       </c>
-      <c r="H85" s="33" t="inlineStr">
+      <c r="H85" s="32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="I85" s="32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
+      <c r="I85" s="33" t="inlineStr">
+        <is>
+          <t>Sin cambios</t>
+        </is>
+      </c>
+      <c r="J85" s="32" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>CAMBIOS APLICADOS AL ITINERARIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="39" t="inlineStr">
+        <is>
+          <t>A) 13 SUSTITUCIONES — puntos que quedaban FUERA del término de Níjar (Cabo de Gata/Almería)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="40" t="inlineStr">
+        <is>
+          <t>Punto ELIMINADO (motivo)</t>
+        </is>
+      </c>
+      <c r="C4" s="40" t="inlineStr">
+        <is>
+          <t>Punto NUEVO (dentro de Níjar)</t>
+        </is>
+      </c>
+      <c r="D4" s="40" t="inlineStr">
+        <is>
+          <t>Coordenadas aprox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>P57-D6</t>
+        </is>
+      </c>
+      <c r="B5" s="38" t="inlineStr">
+        <is>
+          <t>Cabo de Gata pueblo · Plaza pueblo</t>
+        </is>
+      </c>
+      <c r="C5" s="38" t="inlineStr">
+        <is>
+          <t>El Barranquete · Núcleo · pedanía Campo de Níjar</t>
+        </is>
+      </c>
+      <c r="D5" s="38" t="inlineStr">
+        <is>
+          <t>36.8381, -2.1971</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>P58-D6</t>
+        </is>
+      </c>
+      <c r="B6" s="38" t="inlineStr">
+        <is>
+          <t>Cabo de Gata pueblo · Almadraba Monteleva</t>
+        </is>
+      </c>
+      <c r="C6" s="38" t="inlineStr">
+        <is>
+          <t>Ruescas · Núcleo rural</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="inlineStr">
+        <is>
+          <t>36.8162, -2.2246</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="inlineStr">
+        <is>
+          <t>P59-D6</t>
+        </is>
+      </c>
+      <c r="B7" s="38" t="inlineStr">
+        <is>
+          <t>Cabo de Gata pueblo · Iglesia Almadraba</t>
+        </is>
+      </c>
+      <c r="C7" s="38" t="inlineStr">
+        <is>
+          <t>El Viso · Núcleo rural</t>
+        </is>
+      </c>
+      <c r="D7" s="38" t="inlineStr">
+        <is>
+          <t>36.8799, -2.2045</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>P60-D6</t>
+        </is>
+      </c>
+      <c r="B8" s="38" t="inlineStr">
+        <is>
+          <t>Salinas · Centro Visitantes Salinas</t>
+        </is>
+      </c>
+      <c r="C8" s="38" t="inlineStr">
+        <is>
+          <t>Los Grillos · Núcleo (San Isidro de Níjar)</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="inlineStr">
+        <is>
+          <t>36.8919, -2.1933</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>P61-D6</t>
+        </is>
+      </c>
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>Salinas · Mirador flamencos</t>
+        </is>
+      </c>
+      <c r="C9" s="38" t="inlineStr">
+        <is>
+          <t>La Serrata · Núcleo rural</t>
+        </is>
+      </c>
+      <c r="D9" s="38" t="inlineStr">
+        <is>
+          <t>36.8754, -2.1472</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>P62-D6</t>
+        </is>
+      </c>
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>Faro Cabo Gata · Faro extremo sur</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="inlineStr">
+        <is>
+          <t>Boca de los Frailes · Núcleo rural (valle San José)</t>
+        </is>
+      </c>
+      <c r="D10" s="38" t="inlineStr">
+        <is>
+          <t>36.8056, -2.1328</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="37" t="inlineStr">
+        <is>
+          <t>P63-D6</t>
+        </is>
+      </c>
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Faro Cabo Gata · Mirador Vela Blanca</t>
+        </is>
+      </c>
+      <c r="C11" s="38" t="inlineStr">
+        <is>
+          <t>Presillas Bajas · Núcleo rural</t>
+        </is>
+      </c>
+      <c r="D11" s="38" t="inlineStr">
+        <is>
+          <t>36.8154, -2.0931</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>P64-D6</t>
+        </is>
+      </c>
+      <c r="B12" s="38" t="inlineStr">
+        <is>
+          <t>Playa Cabo Gata · Playa pueblo Cabo Gata</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="inlineStr">
+        <is>
+          <t>Cala Higuera · Cala accesible por camino de tierra desde San José</t>
+        </is>
+      </c>
+      <c r="D12" s="38" t="inlineStr">
+        <is>
+          <t>36.7653, -2.1083</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t>P65-D6</t>
+        </is>
+      </c>
+      <c r="B13" s="38" t="inlineStr">
+        <is>
+          <t>Retamar · Núcleo Retamar (límite)</t>
+        </is>
+      </c>
+      <c r="C13" s="38" t="inlineStr">
+        <is>
+          <t>El Romeral · Núcleo norte del término</t>
+        </is>
+      </c>
+      <c r="D13" s="38" t="inlineStr">
+        <is>
+          <t>36.9923, -2.2346</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="37" t="inlineStr">
+        <is>
+          <t>P66-D6</t>
+        </is>
+      </c>
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>Pujaire · Núcleo Pujaire</t>
+        </is>
+      </c>
+      <c r="C14" s="38" t="inlineStr">
+        <is>
+          <t>La Higuera · Núcleo rural</t>
+        </is>
+      </c>
+      <c r="D14" s="38" t="inlineStr">
+        <is>
+          <t>36.9219, -2.0174</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="37" t="inlineStr">
+        <is>
+          <t>P68-D6</t>
+        </is>
+      </c>
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>Camping Cabo Gata · Camping municipal</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>Cortijo del Fraile · Monumento histórico (BIC) · pista de acceso</t>
+        </is>
+      </c>
+      <c r="D15" s="38" t="inlineStr">
+        <is>
+          <t>36.8656, -2.0748</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="37" t="inlineStr">
+        <is>
+          <t>P75-D7</t>
+        </is>
+      </c>
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>Pujaire · Pista a Cabo Gata</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>Cala del Cuervo · Cala junto a la carretera de Las Negras</t>
+        </is>
+      </c>
+      <c r="D16" s="38" t="inlineStr">
+        <is>
+          <t>36.873, -2.0035</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="37" t="inlineStr">
+        <is>
+          <t>P78-D7</t>
+        </is>
+      </c>
+      <c r="B17" s="38" t="inlineStr">
+        <is>
+          <t>Carretera N-340a · Tramo Níjar-Almería</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="inlineStr">
+        <is>
+          <t>Saladar y Leche · Núcleo rural</t>
+        </is>
+      </c>
+      <c r="D17" s="38" t="inlineStr">
+        <is>
+          <t>36.9613, -2.0953</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>B) 6 REUBICACIONES — puntos de acceso difícil movidos a un punto accesible cercano</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t>Punto ELIMINADO (motivo)</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>Punto NUEVO (dentro de Níjar)</t>
+        </is>
+      </c>
+      <c r="D21" s="40" t="inlineStr">
+        <is>
+          <t>Coordenadas aprox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="37" t="inlineStr">
+        <is>
+          <t>P14-D2</t>
+        </is>
+      </c>
+      <c r="B22" s="38" t="inlineStr">
+        <is>
+          <t>Mónsul · Playa Mónsul (orilla)</t>
+        </is>
+      </c>
+      <c r="C22" s="38" t="inlineStr">
+        <is>
+          <t>Mónsul · Mirador de carretera (acceso accesible)</t>
+        </is>
+      </c>
+      <c r="D22" s="38" t="inlineStr">
+        <is>
+          <t>36.7395, -2.1195</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="37" t="inlineStr">
+        <is>
+          <t>P15-D2</t>
+        </is>
+      </c>
+      <c r="B23" s="38" t="inlineStr">
+        <is>
+          <t>Genoveses · Playa Genoveses</t>
+        </is>
+      </c>
+      <c r="C23" s="38" t="inlineStr">
+        <is>
+          <t>Genoveses · Entrada/mirador norte (accesible)</t>
+        </is>
+      </c>
+      <c r="D23" s="38" t="inlineStr">
+        <is>
+          <t>36.7555, -2.1145</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="37" t="inlineStr">
+        <is>
+          <t>P28-D3</t>
+        </is>
+      </c>
+      <c r="B24" s="38" t="inlineStr">
+        <is>
+          <t>Las Negras · Acceso pista San Pedro</t>
+        </is>
+      </c>
+      <c r="C24" s="38" t="inlineStr">
+        <is>
+          <t>Las Negras · Aparcamiento/mirador norte (fin de asfalto)</t>
+        </is>
+      </c>
+      <c r="D24" s="38" t="inlineStr">
+        <is>
+          <t>36.8905, -2.005</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="37" t="inlineStr">
+        <is>
+          <t>P29-D3</t>
+        </is>
+      </c>
+      <c r="B25" s="38" t="inlineStr">
+        <is>
+          <t>Cala San Pedro · Cala virgen (sin acceso vehículo)</t>
+        </is>
+      </c>
+      <c r="C25" s="38" t="inlineStr">
+        <is>
+          <t>Las Negras · Puerto/embarcadero (salida a Cala San Pedro)</t>
+        </is>
+      </c>
+      <c r="D25" s="38" t="inlineStr">
+        <is>
+          <t>36.8872, -2.0068</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="37" t="inlineStr">
+        <is>
+          <t>P35-D4</t>
+        </is>
+      </c>
+      <c r="B26" s="38" t="inlineStr">
+        <is>
+          <t>Cala Enmedio · Punto acceso peatonal</t>
+        </is>
+      </c>
+      <c r="C26" s="38" t="inlineStr">
+        <is>
+          <t>Agua Amarga · Aparcamiento sur (inicio sendero Cala Enmedio)</t>
+        </is>
+      </c>
+      <c r="D26" s="38" t="inlineStr">
+        <is>
+          <t>36.9375, -1.9345</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="37" t="inlineStr">
+        <is>
+          <t>P36-D4</t>
+        </is>
+      </c>
+      <c r="B27" s="38" t="inlineStr">
+        <is>
+          <t>Cala Enmedio · Cala virgen mirador</t>
+        </is>
+      </c>
+      <c r="C27" s="38" t="inlineStr">
+        <is>
+          <t>Agua Amarga · Mirador/zona hotelera sur (accesible)</t>
+        </is>
+      </c>
+      <c r="D27" s="38" t="inlineStr">
+        <is>
+          <t>36.9388, -1.9368</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4850,43 +5510,55 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="41" t="inlineStr">
         <is>
           <t>P14-D2</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="42" t="inlineStr">
         <is>
           <t>Mónsul</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>Playa Mónsul (orilla)</t>
-        </is>
+      <c r="D17" s="42" t="inlineStr">
+        <is>
+          <t>Mirador de carretera (acceso accesible)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>36.7395</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-2.1195</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="41" t="inlineStr">
         <is>
           <t>P15-D2</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>Genoveses</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>Playa Genoveses</t>
-        </is>
+      <c r="D18" s="42" t="inlineStr">
+        <is>
+          <t>Entrada/mirador norte (accesible)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>36.7555</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-2.1145</v>
       </c>
     </row>
     <row r="19">
@@ -5130,43 +5802,55 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="41" t="inlineStr">
         <is>
           <t>P28-D3</t>
         </is>
       </c>
-      <c r="B31" s="17" t="n">
+      <c r="B31" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C31" s="42" t="inlineStr">
         <is>
           <t>Las Negras</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>Acceso pista San Pedro</t>
-        </is>
+      <c r="D31" s="42" t="inlineStr">
+        <is>
+          <t>Aparcamiento/mirador norte (fin de asfalto)</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>36.8905</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-2.005</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="41" t="inlineStr">
         <is>
           <t>P29-D3</t>
         </is>
       </c>
-      <c r="B32" s="17" t="n">
+      <c r="B32" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>Cala San Pedro</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>Cala virgen (sin acceso vehículo)</t>
-        </is>
+      <c r="C32" s="42" t="inlineStr">
+        <is>
+          <t>Las Negras</t>
+        </is>
+      </c>
+      <c r="D32" s="42" t="inlineStr">
+        <is>
+          <t>Puerto/embarcadero (salida a Cala San Pedro)</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>36.8872</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-2.0068</v>
       </c>
     </row>
     <row r="33">
@@ -5270,43 +5954,55 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="41" t="inlineStr">
         <is>
           <t>P35-D4</t>
         </is>
       </c>
-      <c r="B38" s="17" t="n">
+      <c r="B38" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>Cala Enmedio</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>Punto acceso peatonal</t>
-        </is>
+      <c r="C38" s="42" t="inlineStr">
+        <is>
+          <t>Agua Amarga</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="inlineStr">
+        <is>
+          <t>Aparcamiento sur (inicio sendero Cala Enmedio)</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>36.9375</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-1.9345</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="41" t="inlineStr">
         <is>
           <t>P36-D4</t>
         </is>
       </c>
-      <c r="B39" s="17" t="n">
+      <c r="B39" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>Cala Enmedio</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>Cala virgen mirador</t>
-        </is>
+      <c r="C39" s="42" t="inlineStr">
+        <is>
+          <t>Agua Amarga</t>
+        </is>
+      </c>
+      <c r="D39" s="42" t="inlineStr">
+        <is>
+          <t>Mirador/zona hotelera sur (accesible)</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>36.9388</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-1.9368</v>
       </c>
     </row>
     <row r="40">
@@ -5710,203 +6406,263 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="inlineStr">
+      <c r="A60" s="41" t="inlineStr">
         <is>
           <t>P57-D6</t>
         </is>
       </c>
-      <c r="B60" s="17" t="n">
+      <c r="B60" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>Cabo de Gata pueblo</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t>Plaza pueblo</t>
-        </is>
+      <c r="C60" s="42" t="inlineStr">
+        <is>
+          <t>El Barranquete</t>
+        </is>
+      </c>
+      <c r="D60" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo · pedanía Campo de Níjar</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>36.8381</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-2.1971</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="inlineStr">
+      <c r="A61" s="41" t="inlineStr">
         <is>
           <t>P58-D6</t>
         </is>
       </c>
-      <c r="B61" s="17" t="n">
+      <c r="B61" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C61" s="17" t="inlineStr">
-        <is>
-          <t>Cabo de Gata pueblo</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>Almadraba Monteleva</t>
-        </is>
+      <c r="C61" s="42" t="inlineStr">
+        <is>
+          <t>Ruescas</t>
+        </is>
+      </c>
+      <c r="D61" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>36.8162</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-2.2246</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="inlineStr">
+      <c r="A62" s="41" t="inlineStr">
         <is>
           <t>P59-D6</t>
         </is>
       </c>
-      <c r="B62" s="17" t="n">
+      <c r="B62" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>Cabo de Gata pueblo</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
-        <is>
-          <t>Iglesia Almadraba</t>
-        </is>
+      <c r="C62" s="42" t="inlineStr">
+        <is>
+          <t>El Viso</t>
+        </is>
+      </c>
+      <c r="D62" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>36.8799</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-2.2045</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="inlineStr">
+      <c r="A63" s="41" t="inlineStr">
         <is>
           <t>P60-D6</t>
         </is>
       </c>
-      <c r="B63" s="17" t="n">
+      <c r="B63" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>Salinas</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>Centro Visitantes Salinas</t>
-        </is>
+      <c r="C63" s="42" t="inlineStr">
+        <is>
+          <t>Los Grillos</t>
+        </is>
+      </c>
+      <c r="D63" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo (San Isidro de Níjar)</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>36.8919</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-2.1933</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="inlineStr">
+      <c r="A64" s="41" t="inlineStr">
         <is>
           <t>P61-D6</t>
         </is>
       </c>
-      <c r="B64" s="17" t="n">
+      <c r="B64" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>Salinas</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
-        <is>
-          <t>Mirador flamencos</t>
-        </is>
+      <c r="C64" s="42" t="inlineStr">
+        <is>
+          <t>La Serrata</t>
+        </is>
+      </c>
+      <c r="D64" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>36.8754</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-2.1472</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="inlineStr">
+      <c r="A65" s="41" t="inlineStr">
         <is>
           <t>P62-D6</t>
         </is>
       </c>
-      <c r="B65" s="17" t="n">
+      <c r="B65" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>Faro Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
-        <is>
-          <t>Faro extremo sur</t>
-        </is>
+      <c r="C65" s="42" t="inlineStr">
+        <is>
+          <t>Boca de los Frailes</t>
+        </is>
+      </c>
+      <c r="D65" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural (valle San José)</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>36.8056</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-2.1328</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="inlineStr">
+      <c r="A66" s="41" t="inlineStr">
         <is>
           <t>P63-D6</t>
         </is>
       </c>
-      <c r="B66" s="17" t="n">
+      <c r="B66" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C66" s="17" t="inlineStr">
-        <is>
-          <t>Faro Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="inlineStr">
-        <is>
-          <t>Mirador Vela Blanca</t>
-        </is>
+      <c r="C66" s="42" t="inlineStr">
+        <is>
+          <t>Presillas Bajas</t>
+        </is>
+      </c>
+      <c r="D66" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>36.8154</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-2.0931</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="inlineStr">
+      <c r="A67" s="41" t="inlineStr">
         <is>
           <t>P64-D6</t>
         </is>
       </c>
-      <c r="B67" s="17" t="n">
+      <c r="B67" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C67" s="17" t="inlineStr">
-        <is>
-          <t>Playa Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="inlineStr">
-        <is>
-          <t>Playa pueblo Cabo Gata</t>
-        </is>
+      <c r="C67" s="42" t="inlineStr">
+        <is>
+          <t>Cala Higuera</t>
+        </is>
+      </c>
+      <c r="D67" s="42" t="inlineStr">
+        <is>
+          <t>Cala accesible por camino de tierra desde San José</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>36.7653</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-2.1083</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="inlineStr">
+      <c r="A68" s="41" t="inlineStr">
         <is>
           <t>P65-D6</t>
         </is>
       </c>
-      <c r="B68" s="17" t="n">
+      <c r="B68" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C68" s="17" t="inlineStr">
-        <is>
-          <t>Retamar</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="inlineStr">
-        <is>
-          <t>Núcleo Retamar (límite)</t>
-        </is>
+      <c r="C68" s="42" t="inlineStr">
+        <is>
+          <t>El Romeral</t>
+        </is>
+      </c>
+      <c r="D68" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo norte del término</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>36.9923</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-2.2346</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="inlineStr">
+      <c r="A69" s="41" t="inlineStr">
         <is>
           <t>P66-D6</t>
         </is>
       </c>
-      <c r="B69" s="17" t="n">
+      <c r="B69" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C69" s="17" t="inlineStr">
-        <is>
-          <t>Pujaire</t>
-        </is>
-      </c>
-      <c r="D69" s="17" t="inlineStr">
-        <is>
-          <t>Núcleo Pujaire</t>
-        </is>
+      <c r="C69" s="42" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="D69" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>36.9219</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-2.0174</v>
       </c>
     </row>
     <row r="70">
@@ -5930,23 +6686,29 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="inlineStr">
+      <c r="A71" s="41" t="inlineStr">
         <is>
           <t>P68-D6</t>
         </is>
       </c>
-      <c r="B71" s="17" t="n">
+      <c r="B71" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C71" s="17" t="inlineStr">
-        <is>
-          <t>Camping Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D71" s="17" t="inlineStr">
-        <is>
-          <t>Camping municipal</t>
-        </is>
+      <c r="C71" s="42" t="inlineStr">
+        <is>
+          <t>Cortijo del Fraile</t>
+        </is>
+      </c>
+      <c r="D71" s="42" t="inlineStr">
+        <is>
+          <t>Monumento histórico (BIC) · pista de acceso</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>36.8656</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-2.0748</v>
       </c>
     </row>
     <row r="72">
@@ -6070,23 +6832,29 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="inlineStr">
+      <c r="A78" s="41" t="inlineStr">
         <is>
           <t>P75-D7</t>
         </is>
       </c>
-      <c r="B78" s="17" t="n">
+      <c r="B78" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="C78" s="17" t="inlineStr">
-        <is>
-          <t>Pujaire</t>
-        </is>
-      </c>
-      <c r="D78" s="17" t="inlineStr">
-        <is>
-          <t>Pista a Cabo Gata</t>
-        </is>
+      <c r="C78" s="42" t="inlineStr">
+        <is>
+          <t>Cala del Cuervo</t>
+        </is>
+      </c>
+      <c r="D78" s="42" t="inlineStr">
+        <is>
+          <t>Cala junto a la carretera de Las Negras</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>36.873</v>
+      </c>
+      <c r="F78" t="n">
+        <v>-2.0035</v>
       </c>
     </row>
     <row r="79">
@@ -6130,23 +6898,29 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="inlineStr">
+      <c r="A81" s="41" t="inlineStr">
         <is>
           <t>P78-D7</t>
         </is>
       </c>
-      <c r="B81" s="17" t="n">
+      <c r="B81" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="C81" s="17" t="inlineStr">
-        <is>
-          <t>Carretera N-340a</t>
-        </is>
-      </c>
-      <c r="D81" s="17" t="inlineStr">
-        <is>
-          <t>Tramo Níjar-Almería</t>
-        </is>
+      <c r="C81" s="42" t="inlineStr">
+        <is>
+          <t>Saladar y Leche</t>
+        </is>
+      </c>
+      <c r="D81" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>36.9613</v>
+      </c>
+      <c r="F81" t="n">
+        <v>-2.0953</v>
       </c>
     </row>
     <row r="82">
@@ -6207,7 +6981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6600,42 +7374,42 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="41" t="inlineStr">
         <is>
           <t>P14-D2</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="42" t="inlineStr">
         <is>
           <t>Mónsul</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>Playa Mónsul (orilla)</t>
+      <c r="D17" s="42" t="inlineStr">
+        <is>
+          <t>Mirador de carretera (acceso accesible)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="41" t="inlineStr">
         <is>
           <t>P15-D2</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>Genoveses</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>Playa Genoveses</t>
+      <c r="D18" s="42" t="inlineStr">
+        <is>
+          <t>Entrada/mirador norte (accesible)</t>
         </is>
       </c>
     </row>
@@ -6880,42 +7654,42 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="41" t="inlineStr">
         <is>
           <t>P28-D3</t>
         </is>
       </c>
-      <c r="B31" s="17" t="n">
+      <c r="B31" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C31" s="42" t="inlineStr">
         <is>
           <t>Las Negras</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>Acceso pista San Pedro</t>
+      <c r="D31" s="42" t="inlineStr">
+        <is>
+          <t>Aparcamiento/mirador norte (fin de asfalto)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="41" t="inlineStr">
         <is>
           <t>P29-D3</t>
         </is>
       </c>
-      <c r="B32" s="17" t="n">
+      <c r="B32" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>Cala San Pedro</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>Cala virgen (sin acceso vehículo)</t>
+      <c r="C32" s="42" t="inlineStr">
+        <is>
+          <t>Las Negras</t>
+        </is>
+      </c>
+      <c r="D32" s="42" t="inlineStr">
+        <is>
+          <t>Puerto/embarcadero (salida a Cala San Pedro)</t>
         </is>
       </c>
     </row>
@@ -7020,42 +7794,42 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="41" t="inlineStr">
         <is>
           <t>P35-D4</t>
         </is>
       </c>
-      <c r="B38" s="17" t="n">
+      <c r="B38" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>Cala Enmedio</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>Punto acceso peatonal</t>
+      <c r="C38" s="42" t="inlineStr">
+        <is>
+          <t>Agua Amarga</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="inlineStr">
+        <is>
+          <t>Aparcamiento sur (inicio sendero Cala Enmedio)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="41" t="inlineStr">
         <is>
           <t>P36-D4</t>
         </is>
       </c>
-      <c r="B39" s="17" t="n">
+      <c r="B39" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>Cala Enmedio</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>Cala virgen mirador</t>
+      <c r="C39" s="42" t="inlineStr">
+        <is>
+          <t>Agua Amarga</t>
+        </is>
+      </c>
+      <c r="D39" s="42" t="inlineStr">
+        <is>
+          <t>Mirador/zona hotelera sur (accesible)</t>
         </is>
       </c>
     </row>
@@ -7460,202 +8234,202 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="inlineStr">
+      <c r="A60" s="41" t="inlineStr">
         <is>
           <t>P57-D6</t>
         </is>
       </c>
-      <c r="B60" s="17" t="n">
+      <c r="B60" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>Cabo de Gata pueblo</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t>Plaza pueblo</t>
+      <c r="C60" s="42" t="inlineStr">
+        <is>
+          <t>El Barranquete</t>
+        </is>
+      </c>
+      <c r="D60" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo · pedanía Campo de Níjar</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="inlineStr">
+      <c r="A61" s="41" t="inlineStr">
         <is>
           <t>P58-D6</t>
         </is>
       </c>
-      <c r="B61" s="17" t="n">
+      <c r="B61" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C61" s="17" t="inlineStr">
-        <is>
-          <t>Cabo de Gata pueblo</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>Almadraba Monteleva</t>
+      <c r="C61" s="42" t="inlineStr">
+        <is>
+          <t>Ruescas</t>
+        </is>
+      </c>
+      <c r="D61" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="inlineStr">
+      <c r="A62" s="41" t="inlineStr">
         <is>
           <t>P59-D6</t>
         </is>
       </c>
-      <c r="B62" s="17" t="n">
+      <c r="B62" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>Cabo de Gata pueblo</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
-        <is>
-          <t>Iglesia Almadraba</t>
+      <c r="C62" s="42" t="inlineStr">
+        <is>
+          <t>El Viso</t>
+        </is>
+      </c>
+      <c r="D62" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="inlineStr">
+      <c r="A63" s="41" t="inlineStr">
         <is>
           <t>P60-D6</t>
         </is>
       </c>
-      <c r="B63" s="17" t="n">
+      <c r="B63" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>Salinas</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>Centro Visitantes Salinas</t>
+      <c r="C63" s="42" t="inlineStr">
+        <is>
+          <t>Los Grillos</t>
+        </is>
+      </c>
+      <c r="D63" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo (San Isidro de Níjar)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="inlineStr">
+      <c r="A64" s="41" t="inlineStr">
         <is>
           <t>P61-D6</t>
         </is>
       </c>
-      <c r="B64" s="17" t="n">
+      <c r="B64" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>Salinas</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
-        <is>
-          <t>Mirador flamencos</t>
+      <c r="C64" s="42" t="inlineStr">
+        <is>
+          <t>La Serrata</t>
+        </is>
+      </c>
+      <c r="D64" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="inlineStr">
+      <c r="A65" s="41" t="inlineStr">
         <is>
           <t>P62-D6</t>
         </is>
       </c>
-      <c r="B65" s="17" t="n">
+      <c r="B65" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>Faro Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
-        <is>
-          <t>Faro extremo sur</t>
+      <c r="C65" s="42" t="inlineStr">
+        <is>
+          <t>Boca de los Frailes</t>
+        </is>
+      </c>
+      <c r="D65" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural (valle San José)</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="inlineStr">
+      <c r="A66" s="41" t="inlineStr">
         <is>
           <t>P63-D6</t>
         </is>
       </c>
-      <c r="B66" s="17" t="n">
+      <c r="B66" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C66" s="17" t="inlineStr">
-        <is>
-          <t>Faro Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="inlineStr">
-        <is>
-          <t>Mirador Vela Blanca</t>
+      <c r="C66" s="42" t="inlineStr">
+        <is>
+          <t>Presillas Bajas</t>
+        </is>
+      </c>
+      <c r="D66" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="inlineStr">
+      <c r="A67" s="41" t="inlineStr">
         <is>
           <t>P64-D6</t>
         </is>
       </c>
-      <c r="B67" s="17" t="n">
+      <c r="B67" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C67" s="17" t="inlineStr">
-        <is>
-          <t>Playa Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="inlineStr">
-        <is>
-          <t>Playa pueblo Cabo Gata</t>
+      <c r="C67" s="42" t="inlineStr">
+        <is>
+          <t>Cala Higuera</t>
+        </is>
+      </c>
+      <c r="D67" s="42" t="inlineStr">
+        <is>
+          <t>Cala accesible por camino de tierra desde San José</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="inlineStr">
+      <c r="A68" s="41" t="inlineStr">
         <is>
           <t>P65-D6</t>
         </is>
       </c>
-      <c r="B68" s="17" t="n">
+      <c r="B68" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C68" s="17" t="inlineStr">
-        <is>
-          <t>Retamar</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="inlineStr">
-        <is>
-          <t>Núcleo Retamar (límite)</t>
+      <c r="C68" s="42" t="inlineStr">
+        <is>
+          <t>El Romeral</t>
+        </is>
+      </c>
+      <c r="D68" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo norte del término</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="inlineStr">
+      <c r="A69" s="41" t="inlineStr">
         <is>
           <t>P66-D6</t>
         </is>
       </c>
-      <c r="B69" s="17" t="n">
+      <c r="B69" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C69" s="17" t="inlineStr">
-        <is>
-          <t>Pujaire</t>
-        </is>
-      </c>
-      <c r="D69" s="17" t="inlineStr">
-        <is>
-          <t>Núcleo Pujaire</t>
+      <c r="C69" s="42" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="D69" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
         </is>
       </c>
     </row>
@@ -7680,22 +8454,22 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="inlineStr">
+      <c r="A71" s="41" t="inlineStr">
         <is>
           <t>P68-D6</t>
         </is>
       </c>
-      <c r="B71" s="17" t="n">
+      <c r="B71" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C71" s="17" t="inlineStr">
-        <is>
-          <t>Camping Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D71" s="17" t="inlineStr">
-        <is>
-          <t>Camping municipal</t>
+      <c r="C71" s="42" t="inlineStr">
+        <is>
+          <t>Cortijo del Fraile</t>
+        </is>
+      </c>
+      <c r="D71" s="42" t="inlineStr">
+        <is>
+          <t>Monumento histórico (BIC) · pista de acceso</t>
         </is>
       </c>
     </row>
@@ -7820,22 +8594,22 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="inlineStr">
+      <c r="A78" s="41" t="inlineStr">
         <is>
           <t>P75-D7</t>
         </is>
       </c>
-      <c r="B78" s="17" t="n">
+      <c r="B78" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="C78" s="17" t="inlineStr">
-        <is>
-          <t>Pujaire</t>
-        </is>
-      </c>
-      <c r="D78" s="17" t="inlineStr">
-        <is>
-          <t>Pista a Cabo Gata</t>
+      <c r="C78" s="42" t="inlineStr">
+        <is>
+          <t>Cala del Cuervo</t>
+        </is>
+      </c>
+      <c r="D78" s="42" t="inlineStr">
+        <is>
+          <t>Cala junto a la carretera de Las Negras</t>
         </is>
       </c>
     </row>
@@ -7880,22 +8654,22 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="inlineStr">
+      <c r="A81" s="41" t="inlineStr">
         <is>
           <t>P78-D7</t>
         </is>
       </c>
-      <c r="B81" s="17" t="n">
+      <c r="B81" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="C81" s="17" t="inlineStr">
-        <is>
-          <t>Carretera N-340a</t>
-        </is>
-      </c>
-      <c r="D81" s="17" t="inlineStr">
-        <is>
-          <t>Tramo Níjar-Almería</t>
+      <c r="C81" s="42" t="inlineStr">
+        <is>
+          <t>Saladar y Leche</t>
+        </is>
+      </c>
+      <c r="D81" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
         </is>
       </c>
     </row>
@@ -7958,7 +8732,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7986,6 +8760,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="38" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -8299,42 +9074,42 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="41" t="inlineStr">
         <is>
           <t>P14-D2</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="42" t="inlineStr">
         <is>
           <t>Mónsul</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>Playa Mónsul (orilla)</t>
+      <c r="D17" s="42" t="inlineStr">
+        <is>
+          <t>Mirador de carretera (acceso accesible)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="41" t="inlineStr">
         <is>
           <t>P15-D2</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="42" t="inlineStr">
         <is>
           <t>Genoveses</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>Playa Genoveses</t>
+      <c r="D18" s="42" t="inlineStr">
+        <is>
+          <t>Entrada/mirador norte (accesible)</t>
         </is>
       </c>
     </row>
@@ -8579,42 +9354,42 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="41" t="inlineStr">
         <is>
           <t>P28-D3</t>
         </is>
       </c>
-      <c r="B31" s="17" t="n">
+      <c r="B31" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="17" t="inlineStr">
+      <c r="C31" s="42" t="inlineStr">
         <is>
           <t>Las Negras</t>
         </is>
       </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>Acceso pista San Pedro</t>
+      <c r="D31" s="42" t="inlineStr">
+        <is>
+          <t>Aparcamiento/mirador norte (fin de asfalto)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="41" t="inlineStr">
         <is>
           <t>P29-D3</t>
         </is>
       </c>
-      <c r="B32" s="17" t="n">
+      <c r="B32" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>Cala San Pedro</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>Cala virgen (sin acceso vehículo)</t>
+      <c r="C32" s="42" t="inlineStr">
+        <is>
+          <t>Las Negras</t>
+        </is>
+      </c>
+      <c r="D32" s="42" t="inlineStr">
+        <is>
+          <t>Puerto/embarcadero (salida a Cala San Pedro)</t>
         </is>
       </c>
     </row>
@@ -8719,42 +9494,42 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="41" t="inlineStr">
         <is>
           <t>P35-D4</t>
         </is>
       </c>
-      <c r="B38" s="17" t="n">
+      <c r="B38" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>Cala Enmedio</t>
-        </is>
-      </c>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>Punto acceso peatonal</t>
+      <c r="C38" s="42" t="inlineStr">
+        <is>
+          <t>Agua Amarga</t>
+        </is>
+      </c>
+      <c r="D38" s="42" t="inlineStr">
+        <is>
+          <t>Aparcamiento sur (inicio sendero Cala Enmedio)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="41" t="inlineStr">
         <is>
           <t>P36-D4</t>
         </is>
       </c>
-      <c r="B39" s="17" t="n">
+      <c r="B39" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>Cala Enmedio</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>Cala virgen mirador</t>
+      <c r="C39" s="42" t="inlineStr">
+        <is>
+          <t>Agua Amarga</t>
+        </is>
+      </c>
+      <c r="D39" s="42" t="inlineStr">
+        <is>
+          <t>Mirador/zona hotelera sur (accesible)</t>
         </is>
       </c>
     </row>
@@ -9159,202 +9934,202 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="inlineStr">
+      <c r="A60" s="41" t="inlineStr">
         <is>
           <t>P57-D6</t>
         </is>
       </c>
-      <c r="B60" s="17" t="n">
+      <c r="B60" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>Cabo de Gata pueblo</t>
-        </is>
-      </c>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t>Plaza pueblo</t>
+      <c r="C60" s="42" t="inlineStr">
+        <is>
+          <t>El Barranquete</t>
+        </is>
+      </c>
+      <c r="D60" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo · pedanía Campo de Níjar</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="inlineStr">
+      <c r="A61" s="41" t="inlineStr">
         <is>
           <t>P58-D6</t>
         </is>
       </c>
-      <c r="B61" s="17" t="n">
+      <c r="B61" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C61" s="17" t="inlineStr">
-        <is>
-          <t>Cabo de Gata pueblo</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>Almadraba Monteleva</t>
+      <c r="C61" s="42" t="inlineStr">
+        <is>
+          <t>Ruescas</t>
+        </is>
+      </c>
+      <c r="D61" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="inlineStr">
+      <c r="A62" s="41" t="inlineStr">
         <is>
           <t>P59-D6</t>
         </is>
       </c>
-      <c r="B62" s="17" t="n">
+      <c r="B62" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>Cabo de Gata pueblo</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
-        <is>
-          <t>Iglesia Almadraba</t>
+      <c r="C62" s="42" t="inlineStr">
+        <is>
+          <t>El Viso</t>
+        </is>
+      </c>
+      <c r="D62" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="inlineStr">
+      <c r="A63" s="41" t="inlineStr">
         <is>
           <t>P60-D6</t>
         </is>
       </c>
-      <c r="B63" s="17" t="n">
+      <c r="B63" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>Salinas</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>Centro Visitantes Salinas</t>
+      <c r="C63" s="42" t="inlineStr">
+        <is>
+          <t>Los Grillos</t>
+        </is>
+      </c>
+      <c r="D63" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo (San Isidro de Níjar)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="inlineStr">
+      <c r="A64" s="41" t="inlineStr">
         <is>
           <t>P61-D6</t>
         </is>
       </c>
-      <c r="B64" s="17" t="n">
+      <c r="B64" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>Salinas</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
-        <is>
-          <t>Mirador flamencos</t>
+      <c r="C64" s="42" t="inlineStr">
+        <is>
+          <t>La Serrata</t>
+        </is>
+      </c>
+      <c r="D64" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="inlineStr">
+      <c r="A65" s="41" t="inlineStr">
         <is>
           <t>P62-D6</t>
         </is>
       </c>
-      <c r="B65" s="17" t="n">
+      <c r="B65" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>Faro Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
-        <is>
-          <t>Faro extremo sur</t>
+      <c r="C65" s="42" t="inlineStr">
+        <is>
+          <t>Boca de los Frailes</t>
+        </is>
+      </c>
+      <c r="D65" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural (valle San José)</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="16" t="inlineStr">
+      <c r="A66" s="41" t="inlineStr">
         <is>
           <t>P63-D6</t>
         </is>
       </c>
-      <c r="B66" s="17" t="n">
+      <c r="B66" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C66" s="17" t="inlineStr">
-        <is>
-          <t>Faro Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="inlineStr">
-        <is>
-          <t>Mirador Vela Blanca</t>
+      <c r="C66" s="42" t="inlineStr">
+        <is>
+          <t>Presillas Bajas</t>
+        </is>
+      </c>
+      <c r="D66" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="16" t="inlineStr">
+      <c r="A67" s="41" t="inlineStr">
         <is>
           <t>P64-D6</t>
         </is>
       </c>
-      <c r="B67" s="17" t="n">
+      <c r="B67" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C67" s="17" t="inlineStr">
-        <is>
-          <t>Playa Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="inlineStr">
-        <is>
-          <t>Playa pueblo Cabo Gata</t>
+      <c r="C67" s="42" t="inlineStr">
+        <is>
+          <t>Cala Higuera</t>
+        </is>
+      </c>
+      <c r="D67" s="42" t="inlineStr">
+        <is>
+          <t>Cala accesible por camino de tierra desde San José</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="16" t="inlineStr">
+      <c r="A68" s="41" t="inlineStr">
         <is>
           <t>P65-D6</t>
         </is>
       </c>
-      <c r="B68" s="17" t="n">
+      <c r="B68" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C68" s="17" t="inlineStr">
-        <is>
-          <t>Retamar</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="inlineStr">
-        <is>
-          <t>Núcleo Retamar (límite)</t>
+      <c r="C68" s="42" t="inlineStr">
+        <is>
+          <t>El Romeral</t>
+        </is>
+      </c>
+      <c r="D68" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo norte del término</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="inlineStr">
+      <c r="A69" s="41" t="inlineStr">
         <is>
           <t>P66-D6</t>
         </is>
       </c>
-      <c r="B69" s="17" t="n">
+      <c r="B69" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C69" s="17" t="inlineStr">
-        <is>
-          <t>Pujaire</t>
-        </is>
-      </c>
-      <c r="D69" s="17" t="inlineStr">
-        <is>
-          <t>Núcleo Pujaire</t>
+      <c r="C69" s="42" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="D69" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
         </is>
       </c>
     </row>
@@ -9379,22 +10154,22 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="inlineStr">
+      <c r="A71" s="41" t="inlineStr">
         <is>
           <t>P68-D6</t>
         </is>
       </c>
-      <c r="B71" s="17" t="n">
+      <c r="B71" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="C71" s="17" t="inlineStr">
-        <is>
-          <t>Camping Cabo Gata</t>
-        </is>
-      </c>
-      <c r="D71" s="17" t="inlineStr">
-        <is>
-          <t>Camping municipal</t>
+      <c r="C71" s="42" t="inlineStr">
+        <is>
+          <t>Cortijo del Fraile</t>
+        </is>
+      </c>
+      <c r="D71" s="42" t="inlineStr">
+        <is>
+          <t>Monumento histórico (BIC) · pista de acceso</t>
         </is>
       </c>
     </row>
@@ -9519,22 +10294,22 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="inlineStr">
+      <c r="A78" s="41" t="inlineStr">
         <is>
           <t>P75-D7</t>
         </is>
       </c>
-      <c r="B78" s="17" t="n">
+      <c r="B78" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="C78" s="17" t="inlineStr">
-        <is>
-          <t>Pujaire</t>
-        </is>
-      </c>
-      <c r="D78" s="17" t="inlineStr">
-        <is>
-          <t>Pista a Cabo Gata</t>
+      <c r="C78" s="42" t="inlineStr">
+        <is>
+          <t>Cala del Cuervo</t>
+        </is>
+      </c>
+      <c r="D78" s="42" t="inlineStr">
+        <is>
+          <t>Cala junto a la carretera de Las Negras</t>
         </is>
       </c>
     </row>
@@ -9579,22 +10354,22 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="inlineStr">
+      <c r="A81" s="41" t="inlineStr">
         <is>
           <t>P78-D7</t>
         </is>
       </c>
-      <c r="B81" s="17" t="n">
+      <c r="B81" s="42" t="n">
         <v>7</v>
       </c>
-      <c r="C81" s="17" t="inlineStr">
-        <is>
-          <t>Carretera N-340a</t>
-        </is>
-      </c>
-      <c r="D81" s="17" t="inlineStr">
-        <is>
-          <t>Tramo Níjar-Almería</t>
+      <c r="C81" s="42" t="inlineStr">
+        <is>
+          <t>Saladar y Leche</t>
+        </is>
+      </c>
+      <c r="D81" s="42" t="inlineStr">
+        <is>
+          <t>Núcleo rural</t>
         </is>
       </c>
     </row>
@@ -9657,7 +10432,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9981,7 +10756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10223,7 +10998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
